--- a/naver-place-crawler/results_nail/화성_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/화성_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V305"/>
+  <dimension ref="A1:V357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28357,34 +28357,30 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>미용기기,재료</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>조흥인터내셔널</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>ktnetblog@naver.com</t>
-        </is>
-      </c>
+          <t>아델라네일</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
-          <t>0507-1415-0730</t>
+          <t>031-355-9877</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 효행로 1060 E타운4 501호</t>
+          <t>경기도 화성시 만세구 수노을중앙로 126 1동 3층 301호</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>http://imonster.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -28394,7 +28390,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -28415,17 +28411,17 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P301" t="n">
         <v>3</v>
       </c>
       <c r="Q301" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R301" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="S301" t="inlineStr">
         <is>
@@ -28434,12 +28430,12 @@
       </c>
       <c r="T301" t="inlineStr">
         <is>
-          <t>1482540031</t>
+          <t>1441968754</t>
         </is>
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1482540031</t>
+          <t>https://m.place.naver.com/place/1441968754</t>
         </is>
       </c>
       <c r="V301" t="inlineStr">
@@ -28451,34 +28447,30 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>스타일체인지뷰티</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>slaz0317@naver.com</t>
-        </is>
-      </c>
+          <t>꽃보다,너</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
-          <t>031-356-1900</t>
+          <t>0507-1336-0122</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
-          <t>경기도 화성시 만세구 수노을2로 34 백호빌딩 3층</t>
+          <t>경기도 화성시 만세구 향남읍 행정동로 101-1 상가동2층</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/you_over_f_nail?igsh=cXNpZ3o3MG9tOXo3&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -28488,7 +28480,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -28509,18 +28501,18 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P302" t="n">
-        <v>1060</v>
+        <v>12</v>
       </c>
       <c r="Q302" t="n">
+        <v>3</v>
+      </c>
+      <c r="R302" t="n">
         <v>15</v>
       </c>
-      <c r="R302" t="n">
-        <v>1075</v>
-      </c>
       <c r="S302" t="inlineStr">
         <is>
           <t>X</t>
@@ -28528,12 +28520,12 @@
       </c>
       <c r="T302" t="inlineStr">
         <is>
-          <t>1137768811</t>
+          <t>13085445</t>
         </is>
       </c>
       <c r="U302" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137768811</t>
+          <t>https://m.place.naver.com/place/13085445</t>
         </is>
       </c>
       <c r="V302" t="inlineStr">
@@ -28545,34 +28537,30 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>레디투웍스</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>r2w_team@naver.com</t>
-        </is>
-      </c>
+          <t>네일브릭</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
-          <t>0507-1442-5804</t>
+          <t>0507-1456-6714</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 병점노을5로 20 골든스퀘어2차 1411호</t>
+          <t>경기도 화성시 동탄구 동탄순환대로14길 50-16 1층 102호</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/r2w_team</t>
+          <t>https://www.instagram.com/_nailbrick_?igsh=ZW5reHBwaHczcnFv&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -28587,7 +28575,7 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -28607,13 +28595,13 @@
         </is>
       </c>
       <c r="P303" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="Q303" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="R303" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
@@ -28622,12 +28610,12 @@
       </c>
       <c r="T303" t="inlineStr">
         <is>
-          <t>2070950445</t>
+          <t>1958437523</t>
         </is>
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2070950445</t>
+          <t>https://m.place.naver.com/place/1958437523</t>
         </is>
       </c>
       <c r="V303" t="inlineStr">
@@ -28639,34 +28627,34 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>스페이스와이 SPACE Y</t>
+          <t>레푸스 동탄 호수점</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>yonseiblog@naver.com</t>
+          <t>refussdt@naver.com</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
-          <t>0507-1396-3851</t>
+          <t>0507-1395-8871</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄구 동탄대로 599 303호</t>
+          <t>경기도 화성시 동탄구 동탄순환대로 127-5 우성센트럴타워 6층 610호</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/refussdt</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -28676,12 +28664,12 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -28697,17 +28685,17 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P304" t="n">
-        <v>0</v>
+        <v>2282</v>
       </c>
       <c r="Q304" t="n">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="R304" t="n">
-        <v>0</v>
+        <v>2821</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -28716,12 +28704,12 @@
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t>1315149633</t>
+          <t>1178644545</t>
         </is>
       </c>
       <c r="U304" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315149633</t>
+          <t>https://m.place.naver.com/place/1178644545</t>
         </is>
       </c>
       <c r="V304" t="inlineStr">
@@ -28733,34 +28721,30 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>다담인테리어</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>dadam-co@naver.com</t>
-        </is>
-      </c>
+          <t>예쁨</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
-          <t>0507-1405-8487</t>
+          <t>0507-1448-3201</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr">
         <is>
-          <t>경기도 화성시 병점구 병점노을4로 19 13층 1313호</t>
+          <t>경기도 화성시 효행구 봉담읍 와우로 81-3 1층 삼성타운</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dadam-co</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -28770,12 +28754,12 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -28795,30 +28779,4746 @@
         </is>
       </c>
       <c r="P305" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>162</v>
+      </c>
+      <c r="R305" t="n">
+        <v>228</v>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>1423016358</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1423016358</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>네일제이</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>0507-1344-6093</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>경기도 화성시 효행구 융건로 98 1층 104호</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q306" t="n">
         <v>0</v>
       </c>
-      <c r="Q305" t="n">
+      <c r="R306" t="n">
+        <v>34</v>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>1426769167</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1426769167</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>인더네일</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>0507-1425-2313</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 서동탄로 11 서동탄역파크자이2차 상가 2층</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/in._.the_nail</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>256</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>5</v>
+      </c>
+      <c r="R307" t="n">
+        <v>261</v>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>1920842570</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1920842570</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>꼼꼼네일 향남점</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>0507-1435-0956</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 향남읍 행정죽전로1길 22-3 101호</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>3</v>
+      </c>
+      <c r="R308" t="n">
+        <v>326</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>1972967316</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1972967316</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>깔깔네일</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>0507-1382-2147</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 병점노을5로 20 골든스퀘어2차 409호</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ggalggal_nail</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>1</v>
+      </c>
+      <c r="R309" t="n">
+        <v>30</v>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>2052787684</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2052787684</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>뷰티공간수네일</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>0507-1428-2340</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 병점1로 216-13 3층 309호</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bssu_nail?igsh=MXh4c24ydWJ1b3VoeQ%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>28</v>
+      </c>
+      <c r="R310" t="n">
+        <v>121</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>2087814754</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2087814754</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>아이유네일 동탄점</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>0507-1454-5122</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄대로시범길 134 카림애비뉴 지하 이마트에브리데이층 초밥상회쪽 외부상가</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>http://instagram.com/eyeu_lash</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>642</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>141</v>
+      </c>
+      <c r="R311" t="n">
+        <v>783</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>1761932898</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1761932898</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>오르소 네일</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>0507-1312-3874</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>경기도 화성시 효행구 봉담읍 와우로73번길 15-7 근린생활시설 2동 206호</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/orso_nail</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>3</v>
+      </c>
+      <c r="R312" t="n">
+        <v>49</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>2006219725</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2006219725</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>포쉬네일 병점점</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>0507-1436-4142</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 경기대로 985 병점홈플러스 1층</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jaeny_4142?utm_source=ig_web_button_share_sheet&amp;igsh=MXdiczNmZDB1MDQxNw==</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>87</v>
+      </c>
+      <c r="R313" t="n">
+        <v>214</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>20455661</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20455661</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>네일마요</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>0507-1494-9322</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 향남읍 한절이2길 5-23 1층 NAILMAYO</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>https://instagram.com/nailmayo_</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>7</v>
+      </c>
+      <c r="R314" t="n">
+        <v>48</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>1571493480</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1571493480</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>오직유네일</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>0507-1369-9801</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 향남읍 행정남로 99-18 가상가동 202호</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/only.u.nail/</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P315" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>10</v>
+      </c>
+      <c r="R315" t="n">
+        <v>346</v>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>1779826044</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1779826044</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>네일그리다</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>경기도 화성시 효행구 효행로265번길 14 1층 104호</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/neilgrida?igsh=MTloZWJzNXZodGt5eg==</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>0</v>
+      </c>
+      <c r="R316" t="n">
+        <v>6</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>2014561764</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2014561764</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>네일숲 &amp; 속눈썹 봉담점</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>olive322@naver.com</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>0507-1423-5525</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>경기도 화성시 효행구 봉담읍 상리중심상가길 6-4 ST프라자 205호</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/olive322</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>1234</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>423</v>
+      </c>
+      <c r="R317" t="n">
+        <v>1657</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>21387727</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21387727</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>유소브네일</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>o202o2@naver.com</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>0507-1462-7442</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 경기대로 1011 병점역써밋프라움 A동 125호</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/o202o2</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>28</v>
+      </c>
+      <c r="R318" t="n">
+        <v>300</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>1127157172</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1127157172</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>어바웃네일</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄반석로 172 상가1층103동143호</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/about_nail_shin</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>1</v>
+      </c>
+      <c r="R319" t="n">
+        <v>61</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>2004784381</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2004784381</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>숨쉼네일</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>0507-1482-3118</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 병점노을4로 17 204호</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the.sumshim?igsh=MXUxc29raHh1ZDQ1cw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>252</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>23</v>
+      </c>
+      <c r="R320" t="n">
+        <v>275</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>1001918790</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1001918790</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>호미네일</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>gudooya@naver.com</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>0507-1336-3590</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄순환대로22길 46 상가1층 호미네일</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/homeynail23</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>1</v>
+      </c>
+      <c r="R321" t="n">
+        <v>17</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>1824069358</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1824069358</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>넬리네일</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>0507-1345-5186</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 병점노을5로 20 골든스퀘어2차 5층 520호 넬리네일</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nelly.nail__/</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>5</v>
+      </c>
+      <c r="R322" t="n">
+        <v>152</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>2075670788</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2075670788</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>네일도 꽃길</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>0507-1380-2735</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄반송3길 50-10 1층 102호</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lcn_nail_flower</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>111</v>
+      </c>
+      <c r="R323" t="n">
+        <v>144</v>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>1930302052</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1930302052</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>네일하트</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 남양읍 남양로 829 2층 205호 살롱라봄 안</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.heart_sujin</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>0</v>
+      </c>
+      <c r="R324" t="n">
+        <v>27</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>1351965799</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1351965799</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>옹글네일</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>chohee3151@naver.com</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>0507-1331-3959</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 노작로 203 서해더블루PAX 111호 (지하주차장이용가능)</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>http://instagram.com/ongle.nail</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>556</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>314</v>
+      </c>
+      <c r="R325" t="n">
+        <v>870</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>1714631794</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1714631794</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>뷰티업라이프 뷰네일 화성점</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>se201690@naver.com</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>0507-1318-6098</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 꽃내음1길 19-18 2층 210호</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/se201690</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>184</v>
+      </c>
+      <c r="R326" t="n">
+        <v>484</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>1582143199</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1582143199</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>벨뷰티 화성남양점</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>belle_beauty__@naver.com</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>0507-1338-5893</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 남양읍 역골중앙로 118 상가 A동 105호</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>https://zero.gongbiz.kr/shop/S000034646</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P327" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>309</v>
+      </c>
+      <c r="R327" t="n">
+        <v>809</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>1862155781</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1862155781</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>허니네일</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>031-373-7751</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄대로14길 16</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_bk_nail/</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>3</v>
+      </c>
+      <c r="R328" t="n">
+        <v>12</v>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>1739720764</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1739720764</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>별빛네일</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>0507-1354-4095</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄시범한빛길 13-1 102호</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>http://instagram.com/starlight__nail_</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>7</v>
+      </c>
+      <c r="R329" t="n">
+        <v>245</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>1794901339</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1794901339</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>오어네일</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>0507-1449-1820</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 병점노을4로 19 골든스퀘어 1차, 302호</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_orenail</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P330" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>8</v>
+      </c>
+      <c r="R330" t="n">
+        <v>115</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>1594652407</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1594652407</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>효드리네일</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄순환대로12길 12 제이제이파크프라자 3층</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>https://instagram.com/hyodrey_nail</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>531</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>16</v>
+      </c>
+      <c r="R331" t="n">
+        <v>547</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>1276982010</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1276982010</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>네일, 숲</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>0507-1381-5648</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 병점동로42번길 26-2 1층</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_nail_soop</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>2</v>
+      </c>
+      <c r="R332" t="n">
+        <v>62</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>2077209674</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2077209674</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>아이엠네일</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>imnail-im@naver.com</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>031-296-3009</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>경기도 화성시 효행구 봉담읍 상리2길 97 211호</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/imnail-im</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>772</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>10</v>
+      </c>
+      <c r="R333" t="n">
+        <v>782</v>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>1295322908</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1295322908</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>조이네일</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>golf528@naver.com</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0507-1376-8097</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 지산2길 34-5 104호</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/joynail_dongtan</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>1</v>
+      </c>
+      <c r="R334" t="n">
+        <v>229</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>1749287945</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1749287945</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>네일퀸</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 남양읍 시청로 219 대광파인밸리상가동1층102호 퀸네일</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P335" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>0</v>
+      </c>
+      <c r="R335" t="n">
+        <v>23</v>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>1402519923</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1402519923</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>스무살에머물다 진서네일</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>0507-1396-6603</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 향남읍 발안남로55번길 26-5 1층 102호</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_aeJzG</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>49</v>
+      </c>
+      <c r="R336" t="n">
+        <v>134</v>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>1341299383</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1341299383</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>소호네일</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>0507-1330-7822</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 남양읍 역골동로36번길 39</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P337" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>0</v>
+      </c>
+      <c r="R337" t="n">
+        <v>0</v>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>1386856904</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1386856904</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>슈가네일</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>sugar_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>0507-1495-9979</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 향남읍 발안남로55번길 27 1층 110호</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sugar._.nail</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>609</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>94</v>
+      </c>
+      <c r="R338" t="n">
+        <v>703</v>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>1137250909</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1137250909</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>네일미용직업교육기관 미르주네일</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>mireujunail@naver.com</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>0507-1318-8035</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 향남읍 상신하길로298번길 7-21 KT시네마1 6층 미르주 네일</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mireuju__nail</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>35</v>
+      </c>
+      <c r="R339" t="n">
+        <v>76</v>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>1595983545</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1595983545</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>체체네일</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>0507-1486-4177</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄지성로 104</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chex2_nail/</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P340" t="n">
+        <v>411</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>0</v>
+      </c>
+      <c r="R340" t="n">
+        <v>411</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>1466207158</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1466207158</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>아진12</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>0507-1307-3741</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄감배산로 143 유림노르웨이숲 202 D존 1층 172호</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ajin12_nail</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>101</v>
+      </c>
+      <c r="R341" t="n">
+        <v>249</v>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>1071952346</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1071952346</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>네일온도</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄순환대로 400 우성스타시티 A동 2층</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.ondo_</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>10</v>
+      </c>
+      <c r="R342" t="n">
         <v>20</v>
       </c>
-      <c r="R305" t="n">
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>1005241201</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1005241201</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>오투네일</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>0507-1348-1712</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄역로 150 상가 b동 212호</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/o2nail__/</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>1273</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>87</v>
+      </c>
+      <c r="R343" t="n">
+        <v>1360</v>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>1232819690</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1232819690</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>네일행복지수</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 수노을중앙로 142 센타프라자 2층 206호</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xfxnJNs</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>3</v>
+      </c>
+      <c r="R344" t="n">
+        <v>170</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>1124033229</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1124033229</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>네일포시즌 풋풋한리쌤 동탄역점</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>footfoothan7@naver.com</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>0507-1490-0700</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄대로19길 10 신유메디프라자 209호</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/footfoothan7</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P345" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>55</v>
+      </c>
+      <c r="R345" t="n">
+        <v>147</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>1156666061</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1156666061</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>진네일</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 남양읍 역골로 41 101호</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P346" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>0</v>
+      </c>
+      <c r="R346" t="n">
+        <v>16</v>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>1164758253</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1164758253</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>쏭네일</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>0507-1393-8836</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>경기도 화성시 효행구 봉담읍 와우로73번길 6 태천센터 203호</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>http://instagram.com/ssongnail2019</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>42</v>
+      </c>
+      <c r="R347" t="n">
+        <v>168</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>1314230635</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1314230635</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>달네일</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>0507-1412-7971</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 향남읍 한절이2길 5-5 달네일</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>http://instagram.com/hyun0479</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>19</v>
+      </c>
+      <c r="R348" t="n">
+        <v>140</v>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>38677073</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38677073</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>달이네일</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>0507-1333-2490</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 꽃내음1길 21 1동 303호</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xiRpDs</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>172</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>7</v>
+      </c>
+      <c r="R349" t="n">
+        <v>179</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>1477968209</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1477968209</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>시크네일</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>0507-1396-4401</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄반송1길 20-5 1층 101호 Chic.</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chic.nail_</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>303</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>0</v>
+      </c>
+      <c r="R350" t="n">
+        <v>303</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>1395867499</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1395867499</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>가구,인테리어</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>리가데코</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>choin1125@naver.com</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 남양읍 활초길15번길 34-7 리가데코</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>http://www.ligadeco.com</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P351" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>0</v>
+      </c>
+      <c r="R351" t="n">
+        <v>0</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>35822325</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35822325</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>미용기기,재료</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>조흥인터내셔널</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>ktnetblog@naver.com</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>0507-1415-0730</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 효행로 1060 E타운4 501호</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>http://imonster.co.kr/</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>0</v>
+      </c>
+      <c r="R352" t="n">
+        <v>3</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>1482540031</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1482540031</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>스타일체인지뷰티</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>slaz0317@naver.com</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>031-356-1900</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 수노을2로 34 백호빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>1060</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>15</v>
+      </c>
+      <c r="R353" t="n">
+        <v>1075</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>1137768811</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1137768811</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>레디투웍스</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>r2w_team@naver.com</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>0507-1442-5804</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 병점노을5로 20 골든스퀘어2차 1411호</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/r2w_team</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>0</v>
+      </c>
+      <c r="R354" t="n">
+        <v>0</v>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>2070950445</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2070950445</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>스페이스와이 SPACE Y</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>yonseiblog@naver.com</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>0507-1396-3851</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄구 동탄대로 599 303호</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>0</v>
+      </c>
+      <c r="R355" t="n">
+        <v>0</v>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>1315149633</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1315149633</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>다담인테리어</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>dadam-co@naver.com</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>0507-1405-8487</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>경기도 화성시 병점구 병점노을4로 19 13층 1313호</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dadam-co</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P356" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q356" t="n">
         <v>20</v>
       </c>
-      <c r="S305" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T305" t="inlineStr">
+      <c r="R356" t="n">
+        <v>20</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
         <is>
           <t>1183159840</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="U356" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1183159840</t>
         </is>
       </c>
-      <c r="V305" t="inlineStr">
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>피부,체형관리</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>디에이뷰티 화성점</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>jungdb9304@naver.com</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>0507-1340-9304</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 남양읍 역골로 71-21 4층</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xabyxdn</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>90</v>
+      </c>
+      <c r="R357" t="n">
+        <v>213</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>1923511477</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1923511477</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
